--- a/00-TrainRnns/tau-3/Theta/Metricas.xlsx
+++ b/00-TrainRnns/tau-3/Theta/Metricas.xlsx
@@ -470,14 +470,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>model_arch69_r0.9_Ld0.7_Lp0.3_seed1706</t>
+          <t>model_arch66_r0.01_Ld0.3_Lp0.7_seed2756</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.959539585743007</v>
+        <v>0.9171103964845527</v>
       </c>
       <c r="E2" t="n">
-        <v>0.009590467483622139</v>
+        <v>0.01964760029879905</v>
       </c>
     </row>
     <row r="3">
@@ -493,14 +493,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>model_arch83_r0.9_Ld0.7_Lp0.3_seed2756</t>
+          <t>model_arch86_r0.01_Ld0.5_Lp0.5_seed6860</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9580472297209148</v>
+        <v>0.9375924960866089</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009944205629083405</v>
+        <v>0.01479265964045226</v>
       </c>
     </row>
     <row r="4">
@@ -516,14 +516,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch97_r0.01_Ld0.5_Lp0.5_seed238</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9561760148217847</v>
+        <v>0.9152567234281425</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01038774596287705</v>
+        <v>0.02008698263086938</v>
       </c>
     </row>
     <row r="5">
@@ -539,14 +539,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>model_arch81_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch31_r0.9_Ld0.5_Lp0.5_seed6227</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9557856672861367</v>
+        <v>0.918216143535598</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01048027134643262</v>
+        <v>0.01938550137240637</v>
       </c>
     </row>
     <row r="6">
@@ -562,14 +562,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed6351</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9556565419817962</v>
+        <v>0.9367647970733753</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01051087834973032</v>
+        <v>0.01498885190932579</v>
       </c>
     </row>
     <row r="7">
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9594673663107273</v>
+        <v>0.9261905535448981</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00960758589750108</v>
+        <v>0.01749530026350287</v>
       </c>
     </row>
     <row r="8">
@@ -608,14 +608,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>model_arch69_r0.9_Ld0.7_Lp0.3_seed1706</t>
+          <t>model_arch66_r0.01_Ld0.3_Lp0.7_seed2756</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9484947000188031</v>
+        <v>0.9470918318785084</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05251722885058983</v>
+        <v>0.0539476592567413</v>
       </c>
     </row>
     <row r="9">
@@ -631,14 +631,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>model_arch83_r0.9_Ld0.7_Lp0.3_seed2756</t>
+          <t>model_arch86_r0.01_Ld0.5_Lp0.5_seed6860</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8197225007704958</v>
+        <v>0.9253068616422592</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1838194260999212</v>
+        <v>0.07616064059687636</v>
       </c>
     </row>
     <row r="10">
@@ -654,14 +654,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch97_r0.01_Ld0.5_Lp0.5_seed238</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.5184352715889421</v>
+        <v>0.9193427999456751</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4910260702795335</v>
+        <v>0.08224187870466111</v>
       </c>
     </row>
     <row r="11">
@@ -677,14 +677,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>model_arch81_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch31_r0.9_Ld0.5_Lp0.5_seed6227</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.4314841944567294</v>
+        <v>0.9177727204758408</v>
       </c>
       <c r="E11" t="n">
-        <v>0.579685482383235</v>
+        <v>0.08384280565511101</v>
       </c>
     </row>
     <row r="12">
@@ -700,14 +700,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed6351</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.3640254270393288</v>
+        <v>0.9062266625185951</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6484696177582681</v>
+        <v>0.09561570996368149</v>
       </c>
     </row>
     <row r="13">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.7137535832507549</v>
+        <v>0.9327187749162007</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2918703236670687</v>
+        <v>0.06860310485258574</v>
       </c>
     </row>
     <row r="14">
@@ -746,14 +746,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>model_arch69_r0.9_Ld0.7_Lp0.3_seed1706</t>
+          <t>model_arch66_r0.01_Ld0.3_Lp0.7_seed2756</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1921087621090493</v>
+        <v>0.9091531691085251</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1679159786761724</v>
+        <v>0.01888203981342081</v>
       </c>
     </row>
     <row r="15">
@@ -769,14 +769,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>model_arch83_r0.9_Ld0.7_Lp0.3_seed2756</t>
+          <t>model_arch86_r0.01_Ld0.5_Lp0.5_seed6860</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.8600553968457648</v>
+        <v>0.9162182750440881</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02908675561383406</v>
+        <v>0.01741359440644011</v>
       </c>
     </row>
     <row r="16">
@@ -792,14 +792,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch97_r0.01_Ld0.5_Lp0.5_seed238</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.791735381883631</v>
+        <v>0.8887726796880577</v>
       </c>
       <c r="E16" t="n">
-        <v>0.04328671426852358</v>
+        <v>0.02311801820560022</v>
       </c>
     </row>
     <row r="17">
@@ -815,14 +815,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>model_arch81_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch31_r0.9_Ld0.5_Lp0.5_seed6227</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.7897880479158</v>
+        <v>0.9183626476385535</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04369145747365019</v>
+        <v>0.01696789775080363</v>
       </c>
     </row>
     <row r="18">
@@ -838,14 +838,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed6351</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.6729583945257893</v>
+        <v>0.8859071830131761</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06797389137972215</v>
+        <v>0.02371359673893371</v>
       </c>
     </row>
     <row r="19">
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.7059374842477245</v>
+        <v>0.9066851397620946</v>
       </c>
       <c r="E19" t="n">
-        <v>0.06111935964725208</v>
+        <v>0.01939500683629538</v>
       </c>
     </row>
     <row r="20">
@@ -884,14 +884,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>model_arch69_r0.9_Ld0.7_Lp0.3_seed1706</t>
+          <t>model_arch66_r0.01_Ld0.3_Lp0.7_seed2756</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-18.88227854545462</v>
+        <v>-8.608987027598335</v>
       </c>
       <c r="E20" t="n">
-        <v>13.81217459703553</v>
+        <v>6.675341874041878</v>
       </c>
     </row>
     <row r="21">
@@ -907,14 +907,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>model_arch83_r0.9_Ld0.7_Lp0.3_seed2756</t>
+          <t>model_arch86_r0.01_Ld0.5_Lp0.5_seed6860</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-14.01599539009734</v>
+        <v>-11.86492780148842</v>
       </c>
       <c r="E21" t="n">
-        <v>10.43157853372498</v>
+        <v>8.937236673662717</v>
       </c>
     </row>
     <row r="22">
@@ -930,14 +930,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch97_r0.01_Ld0.5_Lp0.5_seed238</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-16.85433981708207</v>
+        <v>-9.395161220368944</v>
       </c>
       <c r="E22" t="n">
-        <v>12.40337008178165</v>
+        <v>7.221495333737452</v>
       </c>
     </row>
     <row r="23">
@@ -953,14 +953,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>model_arch81_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch31_r0.9_Ld0.5_Lp0.5_seed6227</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-16.81470072226417</v>
+        <v>-11.6529478710503</v>
       </c>
       <c r="E23" t="n">
-        <v>12.37583289094903</v>
+        <v>8.789974688393526</v>
       </c>
     </row>
     <row r="24">
@@ -976,14 +976,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed6351</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-22.52219769187018</v>
+        <v>-12.01142185234334</v>
       </c>
       <c r="E24" t="n">
-        <v>16.34081831633791</v>
+        <v>9.039005764323493</v>
       </c>
     </row>
     <row r="25">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-17.7055703541582</v>
+        <v>-10.65244541234185</v>
       </c>
       <c r="E25" t="n">
-        <v>12.99471803888548</v>
+        <v>8.094927859990463</v>
       </c>
     </row>
     <row r="26">
@@ -1022,14 +1022,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>model_arch69_r0.9_Ld0.7_Lp0.3_seed1706</t>
+          <t>model_arch66_r0.01_Ld0.3_Lp0.7_seed2756</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-18.46557822445279</v>
+        <v>-18.85332774622897</v>
       </c>
       <c r="E26" t="n">
-        <v>22.70100350455703</v>
+        <v>23.15320190068142</v>
       </c>
     </row>
     <row r="27">
@@ -1045,14 +1045,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>model_arch83_r0.9_Ld0.7_Lp0.3_seed2756</t>
+          <t>model_arch86_r0.01_Ld0.5_Lp0.5_seed6860</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-18.88625400076683</v>
+        <v>-20.77139585497352</v>
       </c>
       <c r="E27" t="n">
-        <v>23.19160091513848</v>
+        <v>25.3900771867128</v>
       </c>
     </row>
     <row r="28">
@@ -1068,14 +1068,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch97_r0.01_Ld0.5_Lp0.5_seed238</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-17.18053344424871</v>
+        <v>-23.31165482263631</v>
       </c>
       <c r="E28" t="n">
-        <v>21.20236803005158</v>
+        <v>28.35255932119953</v>
       </c>
     </row>
     <row r="29">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>model_arch81_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch31_r0.9_Ld0.5_Lp0.5_seed6227</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-16.43384659688035</v>
+        <v>-21.47017757181591</v>
       </c>
       <c r="E29" t="n">
-        <v>20.33157238537753</v>
+        <v>26.20500526231613</v>
       </c>
     </row>
     <row r="30">
@@ -1114,14 +1114,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed6351</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-16.85192599478384</v>
+        <v>-22.70595041900735</v>
       </c>
       <c r="E30" t="n">
-        <v>20.81914186662046</v>
+        <v>27.64617918540507</v>
       </c>
     </row>
     <row r="31">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-17.52592364488233</v>
+        <v>-21.3933734018083</v>
       </c>
       <c r="E31" t="n">
-        <v>21.60516645014547</v>
+        <v>26.11543526791868</v>
       </c>
     </row>
     <row r="32">
@@ -1160,14 +1160,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>model_arch69_r0.9_Ld0.7_Lp0.3_seed1706</t>
+          <t>model_arch66_r0.01_Ld0.3_Lp0.7_seed2756</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-4.435785456090985</v>
+        <v>0.8221377116286124</v>
       </c>
       <c r="E32" t="n">
-        <v>1.651663953612565</v>
+        <v>0.05404347408172376</v>
       </c>
     </row>
     <row r="33">
@@ -1183,14 +1183,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>model_arch83_r0.9_Ld0.7_Lp0.3_seed2756</t>
+          <t>model_arch86_r0.01_Ld0.5_Lp0.5_seed6860</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.6446387854655405</v>
+        <v>0.8701477593402528</v>
       </c>
       <c r="E33" t="n">
-        <v>0.107976540520168</v>
+        <v>0.039455616290596</v>
       </c>
     </row>
     <row r="34">
@@ -1206,14 +1206,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch97_r0.01_Ld0.5_Lp0.5_seed238</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.5386463285456111</v>
+        <v>0.8830633226371345</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1401823591389501</v>
+        <v>0.03553122109318114</v>
       </c>
     </row>
     <row r="35">
@@ -1229,14 +1229,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>model_arch81_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch31_r0.9_Ld0.5_Lp0.5_seed6227</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.7135739591447623</v>
+        <v>0.8508342298546459</v>
       </c>
       <c r="E35" t="n">
-        <v>0.08703058111435466</v>
+        <v>0.04532403415331095</v>
       </c>
     </row>
     <row r="36">
@@ -1252,14 +1252,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed6351</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.5898224355723288</v>
+        <v>0.8711797555806118</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1246324939087957</v>
+        <v>0.03914204412991502</v>
       </c>
     </row>
     <row r="37">
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.1779509931511113</v>
+        <v>0.8715643852927621</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2497796728150692</v>
+        <v>0.03902517435347173</v>
       </c>
     </row>
     <row r="38">
@@ -1298,14 +1298,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>model_arch69_r0.9_Ld0.7_Lp0.3_seed1706</t>
+          <t>model_arch66_r0.01_Ld0.3_Lp0.7_seed2756</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-3.961330496920531</v>
+        <v>-2.935894100824561</v>
       </c>
       <c r="E38" t="n">
-        <v>1.019475301031203</v>
+        <v>0.808764267116577</v>
       </c>
     </row>
     <row r="39">
@@ -1321,14 +1321,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>model_arch83_r0.9_Ld0.7_Lp0.3_seed2756</t>
+          <t>model_arch86_r0.01_Ld0.5_Lp0.5_seed6860</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-2.893372044993486</v>
+        <v>-3.017311759019679</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8000266541525227</v>
+        <v>0.8254943139556743</v>
       </c>
     </row>
     <row r="40">
@@ -1344,14 +1344,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch97_r0.01_Ld0.5_Lp0.5_seed238</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-3.040704106703997</v>
+        <v>-3.782015320606701</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8303010730925832</v>
+        <v>0.9826288556138957</v>
       </c>
     </row>
     <row r="41">
@@ -1367,14 +1367,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>model_arch81_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch31_r0.9_Ld0.5_Lp0.5_seed6227</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-2.70205143388492</v>
+        <v>-3.498297999630722</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7607132809103162</v>
+        <v>0.9243294132789648</v>
       </c>
     </row>
     <row r="42">
@@ -1390,14 +1390,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed6351</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-3.080993384742871</v>
+        <v>-3.57830087279485</v>
       </c>
       <c r="E42" t="n">
-        <v>0.8385798853753983</v>
+        <v>0.9407687440699664</v>
       </c>
     </row>
     <row r="43">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-3.098247441941712</v>
+        <v>-3.338539046045878</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8421253224648478</v>
+        <v>0.8915014637199842</v>
       </c>
     </row>
     <row r="44">
@@ -1436,14 +1436,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>model_arch69_r0.9_Ld0.7_Lp0.3_seed1706</t>
+          <t>model_arch66_r0.01_Ld0.3_Lp0.7_seed2756</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-1.823072172141853</v>
+        <v>-6.17819889810769</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4829817145177904</v>
+        <v>1.228073035174093</v>
       </c>
     </row>
     <row r="45">
@@ -1459,14 +1459,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>model_arch83_r0.9_Ld0.7_Lp0.3_seed2756</t>
+          <t>model_arch86_r0.01_Ld0.5_Lp0.5_seed6860</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-3.738479144478897</v>
+        <v>-4.920669419831014</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8106766819464128</v>
+        <v>1.012930202671186</v>
       </c>
     </row>
     <row r="46">
@@ -1482,14 +1482,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch97_r0.01_Ld0.5_Lp0.5_seed238</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-3.184801581091163</v>
+        <v>-6.047878090581357</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7159514597243565</v>
+        <v>1.20577726545289</v>
       </c>
     </row>
     <row r="47">
@@ -1505,14 +1505,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>model_arch81_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch31_r0.9_Ld0.5_Lp0.5_seed6227</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-3.108344780272201</v>
+        <v>-5.099292938770008</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7028709451308983</v>
+        <v>1.043489780382904</v>
       </c>
     </row>
     <row r="48">
@@ -1528,14 +1528,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed6351</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-2.675851433760791</v>
+        <v>-6.01207122028294</v>
       </c>
       <c r="E48" t="n">
-        <v>0.628878370631063</v>
+        <v>1.199651292557509</v>
       </c>
     </row>
     <row r="49">
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-2.868302362312409</v>
+        <v>-5.638600671836606</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6618035931420696</v>
+        <v>1.135756558448159</v>
       </c>
     </row>
     <row r="50">
@@ -1574,14 +1574,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>model_arch69_r0.9_Ld0.7_Lp0.3_seed1706</t>
+          <t>model_arch66_r0.01_Ld0.3_Lp0.7_seed2756</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-13.77049737678535</v>
+        <v>-21.10982137781647</v>
       </c>
       <c r="E50" t="n">
-        <v>14.03673807225714</v>
+        <v>21.01146383821678</v>
       </c>
     </row>
     <row r="51">
@@ -1597,14 +1597,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>model_arch83_r0.9_Ld0.7_Lp0.3_seed2756</t>
+          <t>model_arch86_r0.01_Ld0.5_Lp0.5_seed6860</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-17.01091356085874</v>
+        <v>-20.17437358381849</v>
       </c>
       <c r="E51" t="n">
-        <v>17.11617893742592</v>
+        <v>20.12248662034342</v>
       </c>
     </row>
     <row r="52">
@@ -1620,14 +1620,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch97_r0.01_Ld0.5_Lp0.5_seed238</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-14.2027969693496</v>
+        <v>-26.75285314898246</v>
       </c>
       <c r="E52" t="n">
-        <v>14.44756216265676</v>
+        <v>26.37416469281193</v>
       </c>
     </row>
     <row r="53">
@@ -1643,14 +1643,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>model_arch81_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch31_r0.9_Ld0.5_Lp0.5_seed6227</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-14.42872964743537</v>
+        <v>-23.28269603034282</v>
       </c>
       <c r="E53" t="n">
-        <v>14.66227110192633</v>
+        <v>23.07639581601841</v>
       </c>
     </row>
     <row r="54">
@@ -1666,14 +1666,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed6351</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>-14.02255189439618</v>
+        <v>-24.84733793974392</v>
       </c>
       <c r="E54" t="n">
-        <v>14.27627118704534</v>
+        <v>24.5633104471843</v>
       </c>
     </row>
     <row r="55">
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-14.64474611106444</v>
+        <v>-23.17212816906899</v>
       </c>
       <c r="E55" t="n">
-        <v>14.86755643808719</v>
+        <v>22.97132067411089</v>
       </c>
     </row>
     <row r="56">
@@ -1712,14 +1712,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>model_arch69_r0.9_Ld0.7_Lp0.3_seed1706</t>
+          <t>model_arch66_r0.01_Ld0.3_Lp0.7_seed2756</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-6.570922521754525</v>
+        <v>-40.16149164075414</v>
       </c>
       <c r="E56" t="n">
-        <v>4.712328861543534</v>
+        <v>25.61992735833174</v>
       </c>
     </row>
     <row r="57">
@@ -1735,14 +1735,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>model_arch83_r0.9_Ld0.7_Lp0.3_seed2756</t>
+          <t>model_arch86_r0.01_Ld0.5_Lp0.5_seed6860</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-29.59477766934089</v>
+        <v>-34.20240292470669</v>
       </c>
       <c r="E57" t="n">
-        <v>19.04294402821749</v>
+        <v>21.91084360209999</v>
       </c>
     </row>
     <row r="58">
@@ -1758,14 +1758,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch97_r0.01_Ld0.5_Lp0.5_seed238</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>-33.75291585695397</v>
+        <v>-32.01308864020857</v>
       </c>
       <c r="E58" t="n">
-        <v>21.63107176766695</v>
+        <v>20.54816040726006</v>
       </c>
     </row>
     <row r="59">
@@ -1781,14 +1781,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>model_arch81_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch31_r0.9_Ld0.5_Lp0.5_seed6227</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>-33.87895622980245</v>
+        <v>-32.48165800999451</v>
       </c>
       <c r="E59" t="n">
-        <v>21.70952240363462</v>
+        <v>20.83980953701048</v>
       </c>
     </row>
     <row r="60">
@@ -1804,14 +1804,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed6351</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-33.02626207704161</v>
+        <v>-36.67335623364978</v>
       </c>
       <c r="E60" t="n">
-        <v>21.17878453720177</v>
+        <v>23.44882587041682</v>
       </c>
     </row>
     <row r="61">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-25.71376495196244</v>
+        <v>-35.04148386901017</v>
       </c>
       <c r="E61" t="n">
-        <v>16.62730601480911</v>
+        <v>22.43310827191412</v>
       </c>
     </row>
   </sheetData>
@@ -1869,27 +1869,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>model_arch69_r0.9_Ld0.7_Lp0.3_seed1706</t>
+          <t>model_arch31_r0.9_Ld0.5_Lp0.5_seed6227</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>model_arch81_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch66_r0.01_Ld0.3_Lp0.7_seed2756</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>model_arch83_r0.9_Ld0.7_Lp0.3_seed2756</t>
+          <t>model_arch86_r0.01_Ld0.5_Lp0.5_seed6860</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed6351</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch97_r0.01_Ld0.5_Lp0.5_seed238</t>
         </is>
       </c>
     </row>
@@ -1905,22 +1905,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1779509931511113</v>
+        <v>0.8715643852927621</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.435785456090985</v>
+        <v>0.8508342298546459</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7135739591447623</v>
+        <v>0.8221377116286124</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6446387854655405</v>
+        <v>0.8701477593402528</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5898224355723288</v>
+        <v>0.8711797555806118</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5386463285456111</v>
+        <v>0.8830633226371345</v>
       </c>
     </row>
     <row r="3">
@@ -1935,22 +1935,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-3.098247441941712</v>
+        <v>-3.338539046045878</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.961330496920531</v>
+        <v>-3.498297999630722</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.70205143388492</v>
+        <v>-2.935894100824561</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.893372044993486</v>
+        <v>-3.017311759019679</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.080993384742871</v>
+        <v>-3.57830087279485</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.040704106703997</v>
+        <v>-3.782015320606701</v>
       </c>
     </row>
     <row r="4">
@@ -1965,22 +1965,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9594673663107273</v>
+        <v>0.9261905535448981</v>
       </c>
       <c r="D4" t="n">
-        <v>0.959539585743007</v>
+        <v>0.918216143535598</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9557856672861367</v>
+        <v>0.9171103964845527</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9580472297209148</v>
+        <v>0.9375924960866089</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9556565419817962</v>
+        <v>0.9367647970733753</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9561760148217847</v>
+        <v>0.9152567234281425</v>
       </c>
     </row>
     <row r="5">
@@ -1995,22 +1995,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-2.868302362312409</v>
+        <v>-5.638600671836606</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.823072172141853</v>
+        <v>-5.099292938770008</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.108344780272201</v>
+        <v>-6.17819889810769</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.738479144478897</v>
+        <v>-4.920669419831014</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.675851433760791</v>
+        <v>-6.01207122028294</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.184801581091163</v>
+        <v>-6.047878090581357</v>
       </c>
     </row>
     <row r="6">
@@ -2025,22 +2025,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7137535832507549</v>
+        <v>0.9327187749162007</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9484947000188031</v>
+        <v>0.9177727204758408</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4314841944567294</v>
+        <v>0.9470918318785084</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8197225007704958</v>
+        <v>0.9253068616422592</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3640254270393288</v>
+        <v>0.9062266625185951</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5184352715889421</v>
+        <v>0.9193427999456751</v>
       </c>
     </row>
     <row r="7">
@@ -2055,22 +2055,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7059374842477245</v>
+        <v>0.9066851397620946</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1921087621090493</v>
+        <v>0.9183626476385535</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7897880479158</v>
+        <v>0.9091531691085251</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8600553968457648</v>
+        <v>0.9162182750440881</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6729583945257893</v>
+        <v>0.8859071830131761</v>
       </c>
       <c r="H7" t="n">
-        <v>0.791735381883631</v>
+        <v>0.8887726796880577</v>
       </c>
     </row>
     <row r="8">
@@ -2085,22 +2085,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-17.7055703541582</v>
+        <v>-10.65244541234185</v>
       </c>
       <c r="D8" t="n">
-        <v>-18.88227854545462</v>
+        <v>-11.6529478710503</v>
       </c>
       <c r="E8" t="n">
-        <v>-16.81470072226417</v>
+        <v>-8.608987027598335</v>
       </c>
       <c r="F8" t="n">
-        <v>-14.01599539009734</v>
+        <v>-11.86492780148842</v>
       </c>
       <c r="G8" t="n">
-        <v>-22.52219769187018</v>
+        <v>-12.01142185234334</v>
       </c>
       <c r="H8" t="n">
-        <v>-16.85433981708207</v>
+        <v>-9.395161220368944</v>
       </c>
     </row>
     <row r="9">
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-17.52592364488233</v>
+        <v>-21.3933734018083</v>
       </c>
       <c r="D9" t="n">
-        <v>-18.46557822445279</v>
+        <v>-21.47017757181591</v>
       </c>
       <c r="E9" t="n">
-        <v>-16.43384659688035</v>
+        <v>-18.85332774622897</v>
       </c>
       <c r="F9" t="n">
-        <v>-18.88625400076683</v>
+        <v>-20.77139585497352</v>
       </c>
       <c r="G9" t="n">
-        <v>-16.85192599478384</v>
+        <v>-22.70595041900735</v>
       </c>
       <c r="H9" t="n">
-        <v>-17.18053344424871</v>
+        <v>-23.31165482263631</v>
       </c>
     </row>
     <row r="10">
@@ -2145,22 +2145,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-25.71376495196244</v>
+        <v>-35.04148386901017</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.570922521754525</v>
+        <v>-32.48165800999451</v>
       </c>
       <c r="E10" t="n">
-        <v>-33.87895622980245</v>
+        <v>-40.16149164075414</v>
       </c>
       <c r="F10" t="n">
-        <v>-29.59477766934089</v>
+        <v>-34.20240292470669</v>
       </c>
       <c r="G10" t="n">
-        <v>-33.02626207704161</v>
+        <v>-36.67335623364978</v>
       </c>
       <c r="H10" t="n">
-        <v>-33.75291585695397</v>
+        <v>-32.01308864020857</v>
       </c>
     </row>
     <row r="11">
@@ -2175,22 +2175,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-14.64474611106444</v>
+        <v>-23.17212816906899</v>
       </c>
       <c r="D11" t="n">
-        <v>-13.77049737678535</v>
+        <v>-23.28269603034282</v>
       </c>
       <c r="E11" t="n">
-        <v>-14.42872964743537</v>
+        <v>-21.10982137781647</v>
       </c>
       <c r="F11" t="n">
-        <v>-17.01091356085874</v>
+        <v>-20.17437358381849</v>
       </c>
       <c r="G11" t="n">
-        <v>-14.02255189439618</v>
+        <v>-24.84733793974392</v>
       </c>
       <c r="H11" t="n">
-        <v>-14.2027969693496</v>
+        <v>-26.75285314898246</v>
       </c>
     </row>
   </sheetData>
@@ -2225,27 +2225,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>model_arch69_r0.9_Ld0.7_Lp0.3_seed1706</t>
+          <t>model_arch31_r0.9_Ld0.5_Lp0.5_seed6227</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>model_arch81_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch66_r0.01_Ld0.3_Lp0.7_seed2756</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>model_arch83_r0.9_Ld0.7_Lp0.3_seed2756</t>
+          <t>model_arch86_r0.01_Ld0.5_Lp0.5_seed6860</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch95_r0.01_Ld0.7_Lp0.3_seed6351</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>model_arch98_r0.9_Ld0.7_Lp0.3_seed8456</t>
+          <t>model_arch97_r0.01_Ld0.5_Lp0.5_seed238</t>
         </is>
       </c>
     </row>
@@ -2261,22 +2261,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2497796728150692</v>
+        <v>0.03902517435347173</v>
       </c>
       <c r="D2" t="n">
-        <v>1.651663953612565</v>
+        <v>0.04532403415331095</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08703058111435466</v>
+        <v>0.05404347408172376</v>
       </c>
       <c r="F2" t="n">
-        <v>0.107976540520168</v>
+        <v>0.039455616290596</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1246324939087957</v>
+        <v>0.03914204412991502</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1401823591389501</v>
+        <v>0.03553122109318114</v>
       </c>
     </row>
     <row r="3">
@@ -2291,22 +2291,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8421253224648478</v>
+        <v>0.8915014637199842</v>
       </c>
       <c r="D3" t="n">
-        <v>1.019475301031203</v>
+        <v>0.9243294132789648</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7607132809103162</v>
+        <v>0.808764267116577</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8000266541525227</v>
+        <v>0.8254943139556743</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8385798853753983</v>
+        <v>0.9407687440699664</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8303010730925832</v>
+        <v>0.9826288556138957</v>
       </c>
     </row>
     <row r="4">
@@ -2321,22 +2321,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.00960758589750108</v>
+        <v>0.01749530026350287</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009590467483622139</v>
+        <v>0.01938550137240637</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01048027134643262</v>
+        <v>0.01964760029879905</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009944205629083405</v>
+        <v>0.01479265964045226</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01051087834973032</v>
+        <v>0.01498885190932579</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01038774596287705</v>
+        <v>0.02008698263086938</v>
       </c>
     </row>
     <row r="5">
@@ -2351,22 +2351,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6618035931420696</v>
+        <v>1.135756558448159</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4829817145177904</v>
+        <v>1.043489780382904</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7028709451308983</v>
+        <v>1.228073035174093</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8106766819464128</v>
+        <v>1.012930202671186</v>
       </c>
       <c r="G5" t="n">
-        <v>0.628878370631063</v>
+        <v>1.199651292557509</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7159514597243565</v>
+        <v>1.20577726545289</v>
       </c>
     </row>
     <row r="6">
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2918703236670687</v>
+        <v>0.06860310485258574</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05251722885058983</v>
+        <v>0.08384280565511101</v>
       </c>
       <c r="E6" t="n">
-        <v>0.579685482383235</v>
+        <v>0.0539476592567413</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1838194260999212</v>
+        <v>0.07616064059687636</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6484696177582681</v>
+        <v>0.09561570996368149</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4910260702795335</v>
+        <v>0.08224187870466111</v>
       </c>
     </row>
     <row r="7">
@@ -2411,22 +2411,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.06111935964725208</v>
+        <v>0.01939500683629538</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1679159786761724</v>
+        <v>0.01696789775080363</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04369145747365019</v>
+        <v>0.01888203981342081</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02908675561383406</v>
+        <v>0.01741359440644011</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06797389137972215</v>
+        <v>0.02371359673893371</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04328671426852358</v>
+        <v>0.02311801820560022</v>
       </c>
     </row>
     <row r="8">
@@ -2441,22 +2441,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12.99471803888548</v>
+        <v>8.094927859990463</v>
       </c>
       <c r="D8" t="n">
-        <v>13.81217459703553</v>
+        <v>8.789974688393526</v>
       </c>
       <c r="E8" t="n">
-        <v>12.37583289094903</v>
+        <v>6.675341874041878</v>
       </c>
       <c r="F8" t="n">
-        <v>10.43157853372498</v>
+        <v>8.937236673662717</v>
       </c>
       <c r="G8" t="n">
-        <v>16.34081831633791</v>
+        <v>9.039005764323493</v>
       </c>
       <c r="H8" t="n">
-        <v>12.40337008178165</v>
+        <v>7.221495333737452</v>
       </c>
     </row>
     <row r="9">
@@ -2471,22 +2471,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.60516645014547</v>
+        <v>26.11543526791868</v>
       </c>
       <c r="D9" t="n">
-        <v>22.70100350455703</v>
+        <v>26.20500526231613</v>
       </c>
       <c r="E9" t="n">
-        <v>20.33157238537753</v>
+        <v>23.15320190068142</v>
       </c>
       <c r="F9" t="n">
-        <v>23.19160091513848</v>
+        <v>25.3900771867128</v>
       </c>
       <c r="G9" t="n">
-        <v>20.81914186662046</v>
+        <v>27.64617918540507</v>
       </c>
       <c r="H9" t="n">
-        <v>21.20236803005158</v>
+        <v>28.35255932119953</v>
       </c>
     </row>
     <row r="10">
@@ -2501,22 +2501,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.62730601480911</v>
+        <v>22.43310827191412</v>
       </c>
       <c r="D10" t="n">
-        <v>4.712328861543534</v>
+        <v>20.83980953701048</v>
       </c>
       <c r="E10" t="n">
-        <v>21.70952240363462</v>
+        <v>25.61992735833174</v>
       </c>
       <c r="F10" t="n">
-        <v>19.04294402821749</v>
+        <v>21.91084360209999</v>
       </c>
       <c r="G10" t="n">
-        <v>21.17878453720177</v>
+        <v>23.44882587041682</v>
       </c>
       <c r="H10" t="n">
-        <v>21.63107176766695</v>
+        <v>20.54816040726006</v>
       </c>
     </row>
     <row r="11">
@@ -2531,22 +2531,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14.86755643808719</v>
+        <v>22.97132067411089</v>
       </c>
       <c r="D11" t="n">
-        <v>14.03673807225714</v>
+        <v>23.07639581601841</v>
       </c>
       <c r="E11" t="n">
-        <v>14.66227110192633</v>
+        <v>21.01146383821678</v>
       </c>
       <c r="F11" t="n">
-        <v>17.11617893742592</v>
+        <v>20.12248662034342</v>
       </c>
       <c r="G11" t="n">
-        <v>14.27627118704534</v>
+        <v>24.5633104471843</v>
       </c>
       <c r="H11" t="n">
-        <v>14.44756216265676</v>
+        <v>26.37416469281193</v>
       </c>
     </row>
   </sheetData>
